--- a/StructureDefinition-openelis-observation.xlsx
+++ b/StructureDefinition-openelis-observation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$83</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3228" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3310" uniqueCount="627">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T02:24:20+00:00</t>
+    <t>2026-10-12T15:07:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1204,7 +1204,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://digi-uw.github.io/openelis-global2-fhir-ig/StructureDefinition/openelis-practitioner)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1214,13 +1214,13 @@
     <t>Who was responsible for asserting the observed value as "true".</t>
   </si>
   <si>
-    <t>Currently the ordering provider of the sample, not the analyst (see Known Issues).</t>
+    <t>Finalized results only: the user who validated the result, as a display-only Reference. Omitted otherwise.</t>
   </si>
   <si>
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
-    <t>SampleHuman.provider</t>
+    <t>History of the analysis status change to finalized (SystemUser)</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1258,6 +1258,9 @@
 </t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t xml:space="preserve">obs-7
 </t>
   </si>
@@ -1439,6 +1442,18 @@
     <t>PQ.code, MO.currency, PQ.translation.code</t>
   </si>
   <si>
+    <t>Observation.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueString</t>
+  </si>
+  <si>
+    <t>valueString</t>
+  </si>
+  <si>
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
@@ -1717,6 +1732,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -2272,12 +2291,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ81"/>
+  <dimension ref="A1:AQ83"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.6796875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.98046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="19.078125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -7847,7 +7866,7 @@
         <v>84</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>161</v>
+        <v>400</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>393</v>
@@ -7859,42 +7878,42 @@
         <v>96</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>393</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>84</v>
@@ -7916,7 +7935,7 @@
         <v>97</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L46" t="s" s="2">
         <v>395</v>
@@ -7925,7 +7944,7 @@
         <v>396</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O46" t="s" s="2">
         <v>398</v>
@@ -7986,7 +8005,7 @@
         <v>96</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>109</v>
@@ -7998,27 +8017,27 @@
         <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8136,10 +8155,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8259,10 +8278,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8285,19 +8304,19 @@
         <v>97</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8346,7 +8365,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8370,10 +8389,10 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>84</v>
@@ -8384,10 +8403,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8413,20 +8432,20 @@
         <v>117</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q50" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="R50" t="s" s="2">
         <v>84</v>
@@ -8450,10 +8469,10 @@
         <v>188</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -8471,7 +8490,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8495,10 +8514,10 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>84</v>
@@ -8509,10 +8528,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8538,14 +8557,14 @@
         <v>171</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8594,7 +8613,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8618,10 +8637,10 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>84</v>
@@ -8632,10 +8651,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8661,14 +8680,14 @@
         <v>111</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8717,7 +8736,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8726,7 +8745,7 @@
         <v>96</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>109</v>
@@ -8741,10 +8760,10 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>84</v>
@@ -8755,10 +8774,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8784,16 +8803,16 @@
         <v>117</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -8842,7 +8861,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8866,10 +8885,10 @@
         <v>84</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>84</v>
@@ -8880,12 +8899,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="C54" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="D54" t="s" s="2">
         <v>84</v>
       </c>
@@ -8903,22 +8924,22 @@
         <v>84</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="K54" t="s" s="2">
         <v>195</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>460</v>
+        <v>395</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>461</v>
+        <v>396</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>462</v>
+        <v>410</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>463</v>
+        <v>398</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -8943,13 +8964,13 @@
         <v>84</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>200</v>
+        <v>84</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>464</v>
+        <v>84</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>465</v>
+        <v>84</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -8967,7 +8988,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>459</v>
+        <v>393</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8976,7 +8997,7 @@
         <v>96</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>466</v>
+        <v>401</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>109</v>
@@ -8988,38 +9009,40 @@
         <v>84</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>84</v>
+        <v>403</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>140</v>
+        <v>404</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>467</v>
+        <v>405</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>84</v>
+        <v>406</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="C55" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="D55" t="s" s="2">
-        <v>469</v>
+        <v>84</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>84</v>
@@ -9028,22 +9051,22 @@
         <v>84</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>470</v>
+        <v>395</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>471</v>
+        <v>396</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>472</v>
+        <v>410</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>473</v>
+        <v>398</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -9068,13 +9091,13 @@
         <v>84</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>200</v>
+        <v>84</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>474</v>
+        <v>84</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>475</v>
+        <v>84</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>84</v>
@@ -9092,16 +9115,16 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>468</v>
+        <v>393</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>84</v>
+        <v>401</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>109</v>
@@ -9113,27 +9136,27 @@
         <v>84</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>476</v>
+        <v>403</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>477</v>
+        <v>404</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>478</v>
+        <v>405</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>479</v>
+        <v>406</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9144,7 +9167,7 @@
         <v>82</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>84</v>
@@ -9156,19 +9179,19 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>481</v>
+        <v>195</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>482</v>
+        <v>465</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>483</v>
+        <v>466</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>484</v>
+        <v>467</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>485</v>
+        <v>468</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>84</v>
@@ -9193,13 +9216,13 @@
         <v>84</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>84</v>
+        <v>200</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>84</v>
+        <v>469</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>84</v>
+        <v>470</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>84</v>
@@ -9217,16 +9240,16 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>84</v>
+        <v>471</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>109</v>
@@ -9241,10 +9264,10 @@
         <v>84</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>486</v>
+        <v>140</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>84</v>
@@ -9255,21 +9278,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>84</v>
+        <v>474</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>84</v>
@@ -9284,15 +9307,17 @@
         <v>195</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>489</v>
+        <v>475</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>490</v>
+        <v>476</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>477</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>478</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
       </c>
@@ -9316,13 +9341,13 @@
         <v>84</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>304</v>
+        <v>200</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>84</v>
@@ -9340,13 +9365,13 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>84</v>
@@ -9361,27 +9386,27 @@
         <v>84</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>494</v>
+        <v>481</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>495</v>
+        <v>482</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>497</v>
+        <v>484</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9392,7 +9417,7 @@
         <v>82</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>84</v>
@@ -9404,19 +9429,19 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>195</v>
+        <v>486</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9441,13 +9466,13 @@
         <v>84</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>304</v>
+        <v>84</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>503</v>
+        <v>84</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>504</v>
+        <v>84</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9465,13 +9490,13 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>84</v>
@@ -9489,10 +9514,10 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>505</v>
+        <v>491</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>506</v>
+        <v>492</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>84</v>
@@ -9501,12 +9526,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>507</v>
+        <v>493</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>507</v>
+        <v>493</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9520,7 +9545,7 @@
         <v>96</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>84</v>
@@ -9529,16 +9554,16 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>508</v>
+        <v>195</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>509</v>
+        <v>494</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>510</v>
+        <v>495</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>511</v>
+        <v>496</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9564,13 +9589,13 @@
         <v>84</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>84</v>
+        <v>304</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>84</v>
+        <v>497</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>84</v>
+        <v>498</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -9588,7 +9613,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>507</v>
+        <v>493</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9603,33 +9628,33 @@
         <v>109</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>512</v>
+        <v>84</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>515</v>
+        <v>501</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>516</v>
+        <v>502</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9643,7 +9668,7 @@
         <v>96</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>84</v>
@@ -9652,18 +9677,20 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>518</v>
+        <v>195</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>520</v>
+        <v>505</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>506</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>507</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
       </c>
@@ -9687,13 +9714,13 @@
         <v>84</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>84</v>
+        <v>304</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>84</v>
+        <v>508</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>84</v>
+        <v>509</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>84</v>
@@ -9711,7 +9738,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9726,33 +9753,33 @@
         <v>109</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>522</v>
+        <v>84</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>523</v>
+        <v>84</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>524</v>
+        <v>510</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>525</v>
+        <v>511</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>526</v>
+        <v>84</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9763,10 +9790,10 @@
         <v>82</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>84</v>
@@ -9775,20 +9802,18 @@
         <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>530</v>
+        <v>515</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>532</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>84</v>
       </c>
@@ -9836,48 +9861,48 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>533</v>
+        <v>109</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>84</v>
+        <v>517</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>84</v>
+        <v>518</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>534</v>
+        <v>519</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>535</v>
+        <v>520</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>84</v>
+        <v>521</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>536</v>
+        <v>522</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>536</v>
+        <v>522</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9891,7 +9916,7 @@
         <v>96</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>84</v>
@@ -9900,15 +9925,17 @@
         <v>84</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>171</v>
+        <v>523</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>172</v>
+        <v>524</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>526</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -9957,7 +9984,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>174</v>
+        <v>522</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -9969,40 +9996,40 @@
         <v>84</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>84</v>
+        <v>527</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>84</v>
+        <v>528</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>84</v>
+        <v>529</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>175</v>
+        <v>530</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>84</v>
+        <v>531</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -10021,18 +10048,20 @@
         <v>84</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>143</v>
+        <v>533</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>144</v>
+        <v>534</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>178</v>
+        <v>535</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
       </c>
@@ -10080,7 +10109,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>181</v>
+        <v>532</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10092,7 +10121,7 @@
         <v>84</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>148</v>
+        <v>538</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>84</v>
@@ -10104,10 +10133,10 @@
         <v>84</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>84</v>
+        <v>539</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>175</v>
+        <v>540</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>84</v>
@@ -10118,46 +10147,42 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>539</v>
+        <v>84</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>540</v>
+        <v>172</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>84</v>
       </c>
@@ -10205,19 +10230,19 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>542</v>
+        <v>174</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>148</v>
+        <v>84</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>84</v>
@@ -10232,7 +10257,7 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>84</v>
@@ -10243,21 +10268,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>84</v>
@@ -10269,15 +10294,17 @@
         <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>544</v>
+        <v>143</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>545</v>
+        <v>144</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10326,19 +10353,19 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>543</v>
+        <v>181</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>547</v>
+        <v>84</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>84</v>
@@ -10350,10 +10377,10 @@
         <v>84</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>548</v>
+        <v>84</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>549</v>
+        <v>175</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>84</v>
@@ -10364,42 +10391,46 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>84</v>
+        <v>544</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>544</v>
+        <v>143</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>546</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
       </c>
@@ -10447,19 +10478,19 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>547</v>
+        <v>84</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>84</v>
@@ -10471,10 +10502,10 @@
         <v>84</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>548</v>
+        <v>84</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>553</v>
+        <v>140</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>84</v>
@@ -10485,10 +10516,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10511,20 +10542,16 @@
         <v>84</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>195</v>
+        <v>549</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>558</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>84</v>
       </c>
@@ -10548,13 +10575,13 @@
         <v>84</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>559</v>
+        <v>84</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>560</v>
+        <v>84</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>84</v>
@@ -10572,7 +10599,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10581,10 +10608,10 @@
         <v>96</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>84</v>
+        <v>552</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>109</v>
+        <v>553</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>84</v>
@@ -10593,13 +10620,13 @@
         <v>84</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>561</v>
+        <v>84</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>478</v>
+        <v>555</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>84</v>
@@ -10610,10 +10637,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10624,7 +10651,7 @@
         <v>82</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>84</v>
@@ -10636,20 +10663,16 @@
         <v>84</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>195</v>
+        <v>549</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>567</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>84</v>
       </c>
@@ -10673,13 +10696,13 @@
         <v>84</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>304</v>
+        <v>84</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>568</v>
+        <v>84</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>569</v>
+        <v>84</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>84</v>
@@ -10697,19 +10720,19 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>84</v>
+        <v>552</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>109</v>
+        <v>553</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>84</v>
@@ -10718,13 +10741,13 @@
         <v>84</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>561</v>
+        <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>478</v>
+        <v>559</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>84</v>
@@ -10735,10 +10758,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10761,17 +10784,19 @@
         <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>571</v>
+        <v>195</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>562</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>563</v>
+      </c>
       <c r="O69" t="s" s="2">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -10796,13 +10821,13 @@
         <v>84</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>84</v>
+        <v>565</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>84</v>
+        <v>566</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>84</v>
@@ -10820,7 +10845,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -10841,13 +10866,13 @@
         <v>84</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>84</v>
+        <v>567</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>84</v>
+        <v>568</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>575</v>
+        <v>483</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>84</v>
@@ -10858,10 +10883,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10872,7 +10897,7 @@
         <v>82</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>84</v>
@@ -10884,16 +10909,20 @@
         <v>84</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
+        <v>571</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>573</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
       </c>
@@ -10917,13 +10946,13 @@
         <v>84</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>84</v>
+        <v>304</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>84</v>
+        <v>574</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>84</v>
+        <v>575</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -10941,13 +10970,13 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>84</v>
@@ -10962,13 +10991,13 @@
         <v>84</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>84</v>
+        <v>567</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>548</v>
+        <v>568</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>579</v>
+        <v>483</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>84</v>
@@ -10979,10 +11008,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10993,7 +11022,7 @@
         <v>82</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>84</v>
@@ -11002,21 +11031,21 @@
         <v>84</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>579</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" t="s" s="2">
+        <v>580</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
       </c>
@@ -11064,13 +11093,13 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>84</v>
@@ -11088,10 +11117,10 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>585</v>
+        <v>84</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>84</v>
@@ -11102,10 +11131,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11116,7 +11145,7 @@
         <v>82</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>84</v>
@@ -11125,20 +11154,18 @@
         <v>84</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>588</v>
+        <v>171</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>591</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11187,13 +11214,13 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>84</v>
@@ -11211,10 +11238,10 @@
         <v>84</v>
       </c>
       <c r="AN72" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AO72" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>84</v>
@@ -11225,10 +11252,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11251,20 +11278,18 @@
         <v>97</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>528</v>
+        <v>587</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>597</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>84</v>
       </c>
@@ -11312,7 +11337,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11336,10 +11361,10 @@
         <v>84</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>84</v>
@@ -11350,10 +11375,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11364,7 +11389,7 @@
         <v>82</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>84</v>
@@ -11373,18 +11398,20 @@
         <v>84</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>171</v>
+        <v>594</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>172</v>
+        <v>595</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>596</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>597</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>84</v>
@@ -11433,19 +11460,19 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>174</v>
+        <v>593</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>84</v>
@@ -11457,10 +11484,10 @@
         <v>84</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>84</v>
+        <v>591</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>175</v>
+        <v>598</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>84</v>
@@ -11471,14 +11498,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -11494,21 +11521,23 @@
         <v>84</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>143</v>
+        <v>533</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>144</v>
+        <v>600</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>178</v>
+        <v>601</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="O75" s="2"/>
+        <v>602</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>603</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>84</v>
       </c>
@@ -11556,7 +11585,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>181</v>
+        <v>599</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -11568,7 +11597,7 @@
         <v>84</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>148</v>
+        <v>109</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>84</v>
@@ -11580,10 +11609,10 @@
         <v>84</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>84</v>
+        <v>604</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>175</v>
+        <v>605</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>84</v>
@@ -11594,46 +11623,42 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>539</v>
+        <v>84</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>540</v>
+        <v>172</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>84</v>
       </c>
@@ -11681,19 +11706,19 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>542</v>
+        <v>174</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>148</v>
+        <v>84</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>84</v>
@@ -11708,7 +11733,7 @@
         <v>84</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>84</v>
@@ -11719,21 +11744,21 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>84</v>
@@ -11742,23 +11767,21 @@
         <v>84</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>195</v>
+        <v>143</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>604</v>
+        <v>144</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>605</v>
+        <v>178</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>84</v>
       </c>
@@ -11782,13 +11805,13 @@
         <v>84</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>304</v>
+        <v>84</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>305</v>
+        <v>84</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>306</v>
+        <v>84</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>84</v>
@@ -11806,19 +11829,19 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>603</v>
+        <v>181</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>84</v>
@@ -11827,16 +11850,16 @@
         <v>84</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>607</v>
+        <v>84</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>310</v>
+        <v>84</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>311</v>
+        <v>175</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>312</v>
+        <v>84</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -11851,38 +11874,38 @@
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>84</v>
+        <v>544</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="J78" t="s" s="2">
         <v>97</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>609</v>
+        <v>143</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>610</v>
+        <v>545</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>396</v>
+        <v>546</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>611</v>
+        <v>146</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>398</v>
+        <v>152</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>84</v>
@@ -11931,19 +11954,19 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>608</v>
+        <v>547</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>84</v>
@@ -11952,27 +11975,27 @@
         <v>84</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>612</v>
+        <v>84</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>403</v>
+        <v>84</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>404</v>
+        <v>140</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>405</v>
+        <v>84</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11980,7 +12003,7 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>96</v>
@@ -11992,22 +12015,22 @@
         <v>84</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="K79" t="s" s="2">
         <v>195</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>463</v>
+        <v>303</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>84</v>
@@ -12032,13 +12055,13 @@
         <v>84</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>200</v>
+        <v>304</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>464</v>
+        <v>305</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>465</v>
+        <v>306</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>84</v>
@@ -12056,16 +12079,16 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>466</v>
+        <v>84</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>109</v>
@@ -12077,16 +12100,16 @@
         <v>84</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>84</v>
+        <v>613</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>140</v>
+        <v>310</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>467</v>
+        <v>311</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>84</v>
+        <v>312</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
@@ -12094,21 +12117,21 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>469</v>
+        <v>84</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>84</v>
@@ -12117,22 +12140,22 @@
         <v>84</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>195</v>
+        <v>615</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>470</v>
+        <v>616</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>471</v>
+        <v>396</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>472</v>
+        <v>617</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>473</v>
+        <v>398</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>84</v>
@@ -12157,13 +12180,13 @@
         <v>84</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>200</v>
+        <v>84</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>474</v>
+        <v>84</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>475</v>
+        <v>84</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>84</v>
@@ -12181,13 +12204,13 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>84</v>
@@ -12202,27 +12225,27 @@
         <v>84</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>476</v>
+        <v>618</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>477</v>
+        <v>404</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>478</v>
+        <v>405</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>479</v>
+        <v>406</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12233,7 +12256,7 @@
         <v>82</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>84</v>
@@ -12245,19 +12268,19 @@
         <v>84</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>85</v>
+        <v>195</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>531</v>
+        <v>622</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>532</v>
+        <v>468</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>84</v>
@@ -12282,13 +12305,13 @@
         <v>84</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>84</v>
+        <v>200</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>84</v>
+        <v>469</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>84</v>
+        <v>470</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>84</v>
@@ -12306,16 +12329,16 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>84</v>
+        <v>471</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>109</v>
@@ -12330,20 +12353,270 @@
         <v>84</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>534</v>
+        <v>140</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>535</v>
+        <v>472</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ81" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="P82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AP82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ82" t="s" s="2">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="P83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AP83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ83" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ81">
+  <autoFilter ref="A1:AQ83">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12353,7 +12626,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI80">
+  <conditionalFormatting sqref="A2:AI82">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-openelis-observation.xlsx
+++ b/StructureDefinition-openelis-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T15:07:11+00:00</t>
+    <t>2026-10-12T15:22:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openelis-observation.xlsx
+++ b/StructureDefinition-openelis-observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.2.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T15:22:52+00:00</t>
+    <t>2026-10-14T21:19:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1248,7 +1248,7 @@
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
   </si>
   <si>
-    <t>Numeric results: valueQuantity with unit (the test's unit of measure as text). Dictionary (coded) and multi-select results: valueCodeableConcept with a LOINC answer coding when mapped plus an {oe}/dictionary_entry coding. Text results: valueString. Absent while no value is recorded.</t>
+    <t>Numeric results: valueQuantity with unit (the test's unit of measure as text). Dictionary (coded) and multi-select results: valueCodeableConcept with one coding for each code the answer carries in its terminology mappings (LOINC, SNOMED CT, CIEL or OCL; SAME_AS codes first), then an {oe}/dictionary_entry coding. Text results: valueString. Absent while no value is recorded.</t>
   </si>
   <si>
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
